--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8099-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8099-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7029721-2733-41DB-AAE2-5CDC2926D045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDB07582-598B-4E70-8C80-B04933C9F55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E77337F1-5745-4B1F-82E1-0664EEFEB9BD}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{45089F33-77F6-4106-B518-22EA17617BC1}"/>
   </bookViews>
   <sheets>
     <sheet name="8099-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1481,29 +1481,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98041770-E412-49F7-9419-5C1618A1186D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAC7C52-A6D4-42A4-9E44-52A1E68B28C5}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1536,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1573,7 +1572,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1625,7 +1624,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1693,7 +1692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1765,7 +1764,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1837,7 +1836,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2053,7 +2052,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2125,7 +2124,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2197,7 +2196,7 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2269,7 +2268,7 @@
         <v>9.64</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2341,7 +2340,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2413,7 +2412,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2485,7 +2484,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2557,7 +2556,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2629,7 +2628,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2701,7 +2700,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2773,7 +2772,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2845,7 +2844,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2917,7 +2916,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2989,7 +2988,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3061,7 +3060,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3133,7 +3132,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3205,7 +3204,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3277,7 +3276,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3349,7 +3348,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3421,7 +3420,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3493,7 +3492,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36" t="s">
         <v>52</v>
       </c>
